--- a/dashboard/ERB_transport_dashboard.xlsx
+++ b/dashboard/ERB_transport_dashboard.xlsx
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E5" s="6" t="n"/>
       <c r="G5" s="5" t="n">
-        <v>39732</v>
+        <v>39733</v>
       </c>
       <c r="H5" s="6" t="n"/>
       <c r="J5" s="5" t="n">
